--- a/ab_test_data 1.xlsx
+++ b/ab_test_data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70bc40f4acb51064/Documentos/GitHub/Teste-A-B-Site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6852A1D1-6EDB-4766-A942-E5D03CCF1672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45068902-6D71-4650-9371-4FCA12C07295}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{6852A1D1-6EDB-4766-A942-E5D03CCF1672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBB3F55F-3D5D-4578-A2F5-98E17890CBAA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,27 +165,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -255,19 +235,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB68003-7908-4B29-B0A9-9B4CAE714049}" name="Tabela1" displayName="Tabela1" ref="A1:H2306" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:H2306" xr:uid="{8FB68003-7908-4B29-B0A9-9B4CAE714049}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB68003-7908-4B29-B0A9-9B4CAE714049}" name="Tabela1" displayName="Tabela1" ref="A1:H2306" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:H2306" xr:uid="{8FB68003-7908-4B29-B0A9-9B4CAE714049}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{106DB8C9-1CA0-4ED9-A5AC-BEDEFD81D163}" name="user_id"/>
     <tableColumn id="2" xr3:uid="{35EC63C0-33C7-4DC2-ABF6-80312F1C8703}" name="device"/>
     <tableColumn id="3" xr3:uid="{C7DC7A74-A048-4F0C-80FE-0C6C8A322EC2}" name="country"/>
-    <tableColumn id="4" xr3:uid="{0B8DA048-5702-4C84-83CD-B944789718E3}" name="timestamp" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{0B8DA048-5702-4C84-83CD-B944789718E3}" name="timestamp" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{24542058-02DA-41A1-A96C-EE3E0ED546BB}" name="group"/>
     <tableColumn id="6" xr3:uid="{B34CC3BD-870C-47E0-9690-F1F60C06DA09}" name="converted"/>
     <tableColumn id="7" xr3:uid="{D9F2F30F-F7E2-4D0D-AEA0-AA4D7F023D25}" name="session_duration"/>
@@ -599,7 +573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>42</v>
       </c>
@@ -625,7 +599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1650</v>
       </c>
@@ -651,7 +625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1308</v>
       </c>
@@ -677,7 +651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>671</v>
       </c>
@@ -703,7 +677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>51</v>
       </c>
@@ -859,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>158</v>
       </c>
@@ -885,7 +859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>108</v>
       </c>
@@ -937,7 +911,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1450</v>
       </c>
@@ -1067,7 +1041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25</v>
       </c>
@@ -1119,7 +1093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>488</v>
       </c>
@@ -1145,7 +1119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>742</v>
       </c>
@@ -1275,7 +1249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1265</v>
       </c>
@@ -1301,7 +1275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>976</v>
       </c>
@@ -1379,7 +1353,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1133</v>
       </c>
@@ -1405,7 +1379,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>833</v>
       </c>
@@ -1483,7 +1457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1944</v>
       </c>
@@ -1535,7 +1509,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>742</v>
       </c>
@@ -1613,7 +1587,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1483</v>
       </c>
@@ -1873,7 +1847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1123</v>
       </c>
@@ -1896,7 +1870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>629</v>
       </c>
@@ -1922,7 +1896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>710</v>
       </c>
@@ -2052,7 +2026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>919</v>
       </c>
@@ -2078,7 +2052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>161</v>
       </c>
@@ -2234,7 +2208,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1435</v>
       </c>
@@ -2364,7 +2338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1864</v>
       </c>
@@ -2416,7 +2390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1215</v>
       </c>
@@ -2468,7 +2442,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>37</v>
       </c>
@@ -2491,7 +2465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>714</v>
       </c>
@@ -2673,7 +2647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1405</v>
       </c>
@@ -2803,7 +2777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>567</v>
       </c>
@@ -2855,7 +2829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1143</v>
       </c>
@@ -2907,7 +2881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>156</v>
       </c>
@@ -3037,7 +3011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>488</v>
       </c>
@@ -3063,7 +3037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1302</v>
       </c>
@@ -3115,7 +3089,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>178</v>
       </c>
@@ -3167,7 +3141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>699</v>
       </c>
@@ -3219,7 +3193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>824</v>
       </c>
@@ -3245,7 +3219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1443</v>
       </c>
@@ -3323,7 +3297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1405</v>
       </c>
@@ -3401,7 +3375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1435</v>
       </c>
@@ -3531,7 +3505,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>412</v>
       </c>
@@ -3557,7 +3531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>509</v>
       </c>
@@ -3609,7 +3583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>126</v>
       </c>
@@ -3661,7 +3635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1758</v>
       </c>
@@ -3739,7 +3713,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>1840</v>
       </c>
@@ -3791,7 +3765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>1530</v>
       </c>
@@ -3817,7 +3791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>18</v>
       </c>
@@ -3921,7 +3895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>1440</v>
       </c>
@@ -4051,7 +4025,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>823</v>
       </c>
@@ -4155,7 +4129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>952</v>
       </c>
@@ -4337,7 +4311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>285</v>
       </c>
@@ -4441,7 +4415,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>365</v>
       </c>
@@ -4493,7 +4467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>1106</v>
       </c>
@@ -4701,7 +4675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>640</v>
       </c>
@@ -4779,7 +4753,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>360</v>
       </c>
@@ -4831,7 +4805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>761</v>
       </c>
@@ -4857,7 +4831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>1308</v>
       </c>
@@ -4883,7 +4857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>1036</v>
       </c>
@@ -4909,7 +4883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>644</v>
       </c>
@@ -4987,7 +4961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>486</v>
       </c>
@@ -5013,7 +4987,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>38</v>
       </c>
@@ -5091,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>1254</v>
       </c>
@@ -5143,7 +5117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>37</v>
       </c>
@@ -5169,7 +5143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>435</v>
       </c>
@@ -5273,7 +5247,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>69</v>
       </c>
@@ -5377,7 +5351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>1092</v>
       </c>
@@ -5429,7 +5403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>685</v>
       </c>
@@ -5481,7 +5455,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>1649</v>
       </c>
@@ -5507,7 +5481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>986</v>
       </c>
@@ -5793,7 +5767,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>136</v>
       </c>
@@ -5819,7 +5793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>127</v>
       </c>
@@ -5871,7 +5845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>1257</v>
       </c>
@@ -5923,7 +5897,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>1018</v>
       </c>
@@ -5949,7 +5923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>1168</v>
       </c>
@@ -6027,7 +6001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>944</v>
       </c>
@@ -6053,7 +6027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>337</v>
       </c>
@@ -6235,7 +6209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>1768</v>
       </c>
@@ -6261,7 +6235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>505</v>
       </c>
@@ -6339,7 +6313,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>794</v>
       </c>
@@ -6417,7 +6391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>486</v>
       </c>
@@ -6443,7 +6417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>370</v>
       </c>
@@ -6547,7 +6521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>8</v>
       </c>
@@ -6599,7 +6573,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>1603</v>
       </c>
@@ -6651,7 +6625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>151</v>
       </c>
@@ -6677,7 +6651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>1342</v>
       </c>
@@ -6885,7 +6859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>390</v>
       </c>
@@ -6911,7 +6885,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>1073</v>
       </c>
@@ -7015,7 +6989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>1397</v>
       </c>
@@ -7246,7 +7220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>27</v>
       </c>
@@ -7272,7 +7246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>136</v>
       </c>
@@ -7402,7 +7376,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>128</v>
       </c>
@@ -7428,7 +7402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>326</v>
       </c>
@@ -7454,7 +7428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>1043</v>
       </c>
@@ -7506,7 +7480,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>804</v>
       </c>
@@ -7610,7 +7584,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>1800</v>
       </c>
@@ -7636,7 +7610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>1971</v>
       </c>
@@ -7662,7 +7636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>1831</v>
       </c>
@@ -7740,7 +7714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>338</v>
       </c>
@@ -7766,7 +7740,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>1130</v>
       </c>
@@ -7792,7 +7766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>1314</v>
       </c>
@@ -7870,7 +7844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>1224</v>
       </c>
@@ -8026,7 +8000,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>1410</v>
       </c>
@@ -8130,7 +8104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>1484</v>
       </c>
@@ -8286,7 +8260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>1684</v>
       </c>
@@ -8364,7 +8338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>1461</v>
       </c>
@@ -8442,7 +8416,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>687</v>
       </c>
@@ -8520,7 +8494,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>136</v>
       </c>
@@ -8546,7 +8520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>17</v>
       </c>
@@ -8572,7 +8546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>1036</v>
       </c>
@@ -8598,7 +8572,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>1647</v>
       </c>
@@ -8624,7 +8598,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>1485</v>
       </c>
@@ -8650,7 +8624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>1254</v>
       </c>
@@ -8780,7 +8754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>218</v>
       </c>
@@ -8858,7 +8832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>90</v>
       </c>
@@ -8884,7 +8858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>1168</v>
       </c>
@@ -8910,7 +8884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>1840</v>
       </c>
@@ -8936,7 +8910,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>1393</v>
       </c>
@@ -9118,7 +9092,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>149</v>
       </c>
@@ -9144,7 +9118,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>1979</v>
       </c>
@@ -9170,7 +9144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>1255</v>
       </c>
@@ -9326,7 +9300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>1803</v>
       </c>
@@ -9482,7 +9456,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>168</v>
       </c>
@@ -9664,7 +9638,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>656</v>
       </c>
@@ -9716,7 +9690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>560</v>
       </c>
@@ -9794,7 +9768,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>22</v>
       </c>
@@ -9924,7 +9898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>58</v>
       </c>
@@ -9976,7 +9950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>1932</v>
       </c>
@@ -10054,7 +10028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>79</v>
       </c>
@@ -10470,7 +10444,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>1672</v>
       </c>
@@ -10496,7 +10470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>1595</v>
       </c>
@@ -10574,7 +10548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>126</v>
       </c>
@@ -10756,7 +10730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>574</v>
       </c>
@@ -10938,7 +10912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>709</v>
       </c>
@@ -11042,7 +11016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>1901</v>
       </c>
@@ -11120,7 +11094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>1214</v>
       </c>
@@ -11146,7 +11120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>18</v>
       </c>
@@ -11380,7 +11354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>1670</v>
       </c>
@@ -11406,7 +11380,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>1680</v>
       </c>
@@ -11484,7 +11458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>537</v>
       </c>
@@ -11536,7 +11510,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>925</v>
       </c>
@@ -11588,7 +11562,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>1897</v>
       </c>
@@ -11666,7 +11640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>1216</v>
       </c>
@@ -11900,7 +11874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>1450</v>
       </c>
@@ -11978,7 +11952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>488</v>
       </c>
@@ -12030,7 +12004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>1696</v>
       </c>
@@ -12056,7 +12030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>61</v>
       </c>
@@ -12108,7 +12082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>79</v>
       </c>
@@ -12212,7 +12186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>1261</v>
       </c>
@@ -12238,7 +12212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>1018</v>
       </c>
@@ -12290,7 +12264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>1480</v>
       </c>
@@ -12368,7 +12342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>680</v>
       </c>
@@ -12394,7 +12368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>1046</v>
       </c>
@@ -12498,7 +12472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>1157</v>
       </c>
@@ -12628,7 +12602,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>1410</v>
       </c>
@@ -12654,7 +12628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>946</v>
       </c>
@@ -12703,7 +12677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>653</v>
       </c>
@@ -12859,7 +12833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>478</v>
       </c>
@@ -13041,7 +13015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>1593</v>
       </c>
@@ -13171,7 +13145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>1793</v>
       </c>
@@ -13249,7 +13223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>1231</v>
       </c>
@@ -13457,7 +13431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>1453</v>
       </c>
@@ -13665,7 +13639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>1483</v>
       </c>
@@ -13691,7 +13665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>957</v>
       </c>
@@ -13714,7 +13688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>981</v>
       </c>
@@ -13740,7 +13714,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>47</v>
       </c>
@@ -13789,7 +13763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>1806</v>
       </c>
@@ -13867,7 +13841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>518</v>
       </c>
@@ -13893,7 +13867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>1254</v>
       </c>
@@ -13945,7 +13919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>740</v>
       </c>
@@ -14049,7 +14023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>521</v>
       </c>
@@ -14075,7 +14049,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>1752</v>
       </c>
@@ -14231,7 +14205,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>261</v>
       </c>
@@ -14257,7 +14231,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>1244</v>
       </c>
@@ -14283,7 +14257,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>1531</v>
       </c>
@@ -14309,7 +14283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>202</v>
       </c>
@@ -14335,7 +14309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>122</v>
       </c>
@@ -14543,7 +14517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>1402</v>
       </c>
@@ -14621,7 +14595,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>218</v>
       </c>
@@ -14647,7 +14621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>1228</v>
       </c>
@@ -14699,7 +14673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>358</v>
       </c>
@@ -14751,7 +14725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>1896</v>
       </c>
@@ -14777,7 +14751,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>887</v>
       </c>
@@ -14803,7 +14777,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>1143</v>
       </c>
@@ -14829,7 +14803,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>1181</v>
       </c>
@@ -14855,7 +14829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>900</v>
       </c>
@@ -14933,7 +14907,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>613</v>
       </c>
@@ -14959,7 +14933,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>145</v>
       </c>
@@ -14985,7 +14959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>1298</v>
       </c>
@@ -15037,7 +15011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>1109</v>
       </c>
@@ -15349,7 +15323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>379</v>
       </c>
@@ -15375,7 +15349,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>1637</v>
       </c>
@@ -15531,7 +15505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>406</v>
       </c>
@@ -15609,7 +15583,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>1489</v>
       </c>
@@ -15791,7 +15765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>12</v>
       </c>
@@ -15817,7 +15791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>140</v>
       </c>
@@ -15843,7 +15817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>1407</v>
       </c>
@@ -15892,7 +15866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>1139</v>
       </c>
@@ -15970,7 +15944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>700</v>
       </c>
@@ -16097,7 +16071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>597</v>
       </c>
@@ -16149,7 +16123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>1051</v>
       </c>
@@ -16331,7 +16305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>522</v>
       </c>
@@ -16357,7 +16331,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>1401</v>
       </c>
@@ -16461,7 +16435,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>1979</v>
       </c>
@@ -16484,7 +16458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>257</v>
       </c>
@@ -16510,7 +16484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>1947</v>
       </c>
@@ -16536,7 +16510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>1489</v>
       </c>
@@ -16562,7 +16536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>1631</v>
       </c>
@@ -16588,7 +16562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>1109</v>
       </c>
@@ -16614,7 +16588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>1137</v>
       </c>
@@ -16819,7 +16793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>1307</v>
       </c>
@@ -16845,7 +16819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>402</v>
       </c>
@@ -16897,7 +16871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>1666</v>
       </c>
@@ -16975,7 +16949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>460</v>
       </c>
@@ -17027,7 +17001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>823</v>
       </c>
@@ -17053,7 +17027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>1603</v>
       </c>
@@ -17209,7 +17183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>1970</v>
       </c>
@@ -17235,7 +17209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>39</v>
       </c>
@@ -17313,7 +17287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>385</v>
       </c>
@@ -17391,7 +17365,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>645</v>
       </c>
@@ -17417,7 +17391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>1550</v>
       </c>
@@ -17469,7 +17443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>454</v>
       </c>
@@ -17573,7 +17547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>1990</v>
       </c>
@@ -17599,7 +17573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>1439</v>
       </c>
@@ -17625,7 +17599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>563</v>
       </c>
@@ -17651,7 +17625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>1891</v>
       </c>
@@ -17703,7 +17677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>1051</v>
       </c>
@@ -17729,7 +17703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>1106</v>
       </c>
@@ -17755,7 +17729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>1130</v>
       </c>
@@ -17781,7 +17755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>1490</v>
       </c>
@@ -17807,7 +17781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A665">
         <v>1121</v>
       </c>
@@ -17859,7 +17833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>547</v>
       </c>
@@ -17911,7 +17885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>1276</v>
       </c>
@@ -17963,7 +17937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>1167</v>
       </c>
@@ -18015,7 +17989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>264</v>
       </c>
@@ -18119,7 +18093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>697</v>
       </c>
@@ -18197,7 +18171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>891</v>
       </c>
@@ -18249,7 +18223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>867</v>
       </c>
@@ -18275,7 +18249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>1940</v>
       </c>
@@ -18431,7 +18405,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>1031</v>
       </c>
@@ -18457,7 +18431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>804</v>
       </c>
@@ -18509,7 +18483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>1453</v>
       </c>
@@ -18535,7 +18509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>1501</v>
       </c>
@@ -18613,7 +18587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>666</v>
       </c>
@@ -18769,7 +18743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>993</v>
       </c>
@@ -18951,7 +18925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>687</v>
       </c>
@@ -19003,7 +18977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>1751</v>
       </c>
@@ -19081,7 +19055,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>1031</v>
       </c>
@@ -19107,7 +19081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>929</v>
       </c>
@@ -19237,7 +19211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>1540</v>
       </c>
@@ -19341,7 +19315,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A724">
         <v>1151</v>
       </c>
@@ -19419,7 +19393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>1026</v>
       </c>
@@ -19445,7 +19419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>1715</v>
       </c>
@@ -19497,7 +19471,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>1896</v>
       </c>
@@ -19523,7 +19497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>128</v>
       </c>
@@ -19653,7 +19627,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A736">
         <v>1560</v>
       </c>
@@ -19679,7 +19653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A737">
         <v>459</v>
       </c>
@@ -19705,7 +19679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>518</v>
       </c>
@@ -19731,7 +19705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>516</v>
       </c>
@@ -19757,7 +19731,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>75</v>
       </c>
@@ -19809,7 +19783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>719</v>
       </c>
@@ -19835,7 +19809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>1082</v>
       </c>
@@ -19887,7 +19861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A745">
         <v>396</v>
       </c>
@@ -20069,7 +20043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="752" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>1405</v>
       </c>
@@ -20095,7 +20069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="753" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>879</v>
       </c>
@@ -20121,7 +20095,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="754" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>936</v>
       </c>
@@ -20144,7 +20118,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="755" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>1864</v>
       </c>
@@ -20170,7 +20144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="756" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A756">
         <v>1067</v>
       </c>
@@ -20196,7 +20170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="757" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>476</v>
       </c>
@@ -20222,7 +20196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="758" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>339</v>
       </c>
@@ -20274,7 +20248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="760" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>453</v>
       </c>
@@ -20378,7 +20352,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="764" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>1669</v>
       </c>
@@ -20404,7 +20378,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="765" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>1143</v>
       </c>
@@ -20430,7 +20404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="766" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>1063</v>
       </c>
@@ -20482,7 +20456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="768" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>992</v>
       </c>
@@ -20534,7 +20508,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A770">
         <v>1326</v>
       </c>
@@ -20560,7 +20534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A771">
         <v>239</v>
       </c>
@@ -20586,7 +20560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>1999</v>
       </c>
@@ -20638,7 +20612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>1247</v>
       </c>
@@ -20742,7 +20716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="778" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>1278</v>
       </c>
@@ -20820,7 +20794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="781" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A781">
         <v>1106</v>
       </c>
@@ -20846,7 +20820,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="782" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A782">
         <v>925</v>
       </c>
@@ -20872,7 +20846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="783" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A783">
         <v>634</v>
       </c>
@@ -20976,7 +20950,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="787" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A787">
         <v>575</v>
       </c>
@@ -21002,7 +20976,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="788" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A788">
         <v>1313</v>
       </c>
@@ -21132,7 +21106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="793" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A793">
         <v>1124</v>
       </c>
@@ -21158,7 +21132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="794" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A794">
         <v>422</v>
       </c>
@@ -21236,7 +21210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="797" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A797">
         <v>5</v>
       </c>
@@ -21262,7 +21236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="798" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A798">
         <v>559</v>
       </c>
@@ -21314,7 +21288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="800" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A800">
         <v>525</v>
       </c>
@@ -21418,7 +21392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="804" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A804">
         <v>1453</v>
       </c>
@@ -21470,7 +21444,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="806" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A806">
         <v>1524</v>
       </c>
@@ -21496,7 +21470,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="807" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A807">
         <v>1907</v>
       </c>
@@ -21522,7 +21496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="808" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A808">
         <v>560</v>
       </c>
@@ -21574,7 +21548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="810" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A810">
         <v>1840</v>
       </c>
@@ -21600,7 +21574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="811" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A811">
         <v>271</v>
       </c>
@@ -21730,7 +21704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="816" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A816">
         <v>1168</v>
       </c>
@@ -21808,7 +21782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="819" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A819">
         <v>511</v>
       </c>
@@ -21860,7 +21834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="821" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A821">
         <v>575</v>
       </c>
@@ -21883,7 +21857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="822" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A822">
         <v>1689</v>
       </c>
@@ -21961,7 +21935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="825" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A825">
         <v>500</v>
       </c>
@@ -22039,7 +22013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="828" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A828">
         <v>1985</v>
       </c>
@@ -22143,7 +22117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="832" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A832">
         <v>1442</v>
       </c>
@@ -22377,7 +22351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="841" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A841">
         <v>939</v>
       </c>
@@ -22403,7 +22377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A842">
         <v>907</v>
       </c>
@@ -22429,7 +22403,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="843" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A843">
         <v>1485</v>
       </c>
@@ -22507,7 +22481,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="846" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A846">
         <v>167</v>
       </c>
@@ -22585,7 +22559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="849" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A849">
         <v>928</v>
       </c>
@@ -22767,7 +22741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="856" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A856">
         <v>886</v>
       </c>
@@ -22845,7 +22819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="859" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A859">
         <v>935</v>
       </c>
@@ -22923,7 +22897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="862" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A862">
         <v>795</v>
       </c>
@@ -23001,7 +22975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="865" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A865">
         <v>971</v>
       </c>
@@ -23053,7 +23027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="867" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A867">
         <v>1830</v>
       </c>
@@ -23209,7 +23183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="873" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A873">
         <v>700</v>
       </c>
@@ -23235,7 +23209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="874" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A874">
         <v>1686</v>
       </c>
@@ -23261,7 +23235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="875" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A875">
         <v>1482</v>
       </c>
@@ -23287,7 +23261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="876" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A876">
         <v>1149</v>
       </c>
@@ -23339,7 +23313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="878" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A878">
         <v>1410</v>
       </c>
@@ -23443,7 +23417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="882" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A882">
         <v>1864</v>
       </c>
@@ -23547,7 +23521,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="886" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A886">
         <v>1399</v>
       </c>
@@ -23651,7 +23625,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="890" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A890">
         <v>238</v>
       </c>
@@ -23677,7 +23651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="891" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A891">
         <v>1650</v>
       </c>
@@ -23703,7 +23677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="892" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A892">
         <v>1306</v>
       </c>
@@ -23781,7 +23755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="895" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A895">
         <v>1051</v>
       </c>
@@ -23833,7 +23807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="897" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A897">
         <v>268</v>
       </c>
@@ -24145,7 +24119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="909" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A909">
         <v>1130</v>
       </c>
@@ -24197,7 +24171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="911" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A911">
         <v>475</v>
       </c>
@@ -24249,7 +24223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="913" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A913">
         <v>1393</v>
       </c>
@@ -24275,7 +24249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="914" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A914">
         <v>1435</v>
       </c>
@@ -24301,7 +24275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="915" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A915">
         <v>653</v>
       </c>
@@ -24379,7 +24353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="918" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A918">
         <v>1327</v>
       </c>
@@ -24431,7 +24405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="920" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A920">
         <v>661</v>
       </c>
@@ -24509,7 +24483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="923" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A923">
         <v>1482</v>
       </c>
@@ -24587,7 +24561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="926" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A926">
         <v>1435</v>
       </c>
@@ -24795,7 +24769,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="934" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A934">
         <v>719</v>
       </c>
@@ -24847,7 +24821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="936" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A936">
         <v>1680</v>
       </c>
@@ -24873,7 +24847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="937" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A937">
         <v>697</v>
       </c>
@@ -24899,7 +24873,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="938" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A938">
         <v>1782</v>
       </c>
@@ -24977,7 +24951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="941" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A941">
         <v>1277</v>
       </c>
@@ -25159,7 +25133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A948">
         <v>1013</v>
       </c>
@@ -25185,7 +25159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A949">
         <v>1161</v>
       </c>
@@ -25208,7 +25182,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="950" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A950">
         <v>1465</v>
       </c>
@@ -25260,7 +25234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="952" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A952">
         <v>1395</v>
       </c>
@@ -25312,7 +25286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="954" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A954">
         <v>1265</v>
       </c>
@@ -25416,7 +25390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="958" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A958">
         <v>1241</v>
       </c>
@@ -25442,7 +25416,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A959">
         <v>1456</v>
       </c>
@@ -25494,7 +25468,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="961" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A961">
         <v>1298</v>
       </c>
@@ -25572,7 +25546,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="964" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A964">
         <v>1247</v>
       </c>
@@ -25754,7 +25728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="971" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A971">
         <v>1168</v>
       </c>
@@ -25780,7 +25754,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="972" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A972">
         <v>1147</v>
       </c>
@@ -25829,7 +25803,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="974" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A974">
         <v>136</v>
       </c>
@@ -25933,7 +25907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="978" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A978">
         <v>123</v>
       </c>
@@ -26089,7 +26063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="984" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A984">
         <v>601</v>
       </c>
@@ -26297,7 +26271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="992" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A992">
         <v>7</v>
       </c>
@@ -26349,7 +26323,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="994" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A994">
         <v>1840</v>
       </c>
@@ -26427,7 +26401,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="997" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A997">
         <v>587</v>
       </c>
@@ -26505,7 +26479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1000" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1000">
         <v>639</v>
       </c>
@@ -26557,7 +26531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1002" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1002">
         <v>1435</v>
       </c>
@@ -26687,7 +26661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1007" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1007">
         <v>1456</v>
       </c>
@@ -26713,7 +26687,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1008" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1008">
         <v>215</v>
       </c>
@@ -26765,7 +26739,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1010" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1010">
         <v>982</v>
       </c>
@@ -26791,7 +26765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1011" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1011">
         <v>236</v>
       </c>
@@ -26895,7 +26869,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1015" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1015">
         <v>521</v>
       </c>
@@ -26973,7 +26947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1018" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1018">
         <v>900</v>
       </c>
@@ -27207,7 +27181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1027" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1027" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1027">
         <v>1293</v>
       </c>
@@ -27363,7 +27337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1033" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1033" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1033">
         <v>1853</v>
       </c>
@@ -27389,7 +27363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1034" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1034" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1034">
         <v>691</v>
       </c>
@@ -27597,7 +27571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1042" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1042">
         <v>194</v>
       </c>
@@ -27779,7 +27753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1049" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1049" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1049">
         <v>1446</v>
       </c>
@@ -27805,7 +27779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1050" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1050">
         <v>1842</v>
       </c>
@@ -27831,7 +27805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1051" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1051">
         <v>1930</v>
       </c>
@@ -27857,7 +27831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1052" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1052">
         <v>155</v>
       </c>
@@ -27883,7 +27857,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1053" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1053" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1053">
         <v>1039</v>
       </c>
@@ -27909,7 +27883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1054" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1054">
         <v>1309</v>
       </c>
@@ -27935,7 +27909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1055" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1055" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1055">
         <v>1728</v>
       </c>
@@ -27961,7 +27935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1056" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1056">
         <v>1709</v>
       </c>
@@ -27987,7 +27961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1057" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1057">
         <v>742</v>
       </c>
@@ -28117,7 +28091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1062" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1062" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1062">
         <v>161</v>
       </c>
@@ -28169,7 +28143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1064" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1064">
         <v>1378</v>
       </c>
@@ -28351,7 +28325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1071" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1071" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1071">
         <v>1395</v>
       </c>
@@ -28377,7 +28351,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1072" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1072" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1072">
         <v>785</v>
       </c>
@@ -28403,7 +28377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1073" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1073">
         <v>1179</v>
       </c>
@@ -28455,7 +28429,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1075" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1075" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1075">
         <v>1936</v>
       </c>
@@ -28481,7 +28455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1076" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1076" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1076">
         <v>1109</v>
       </c>
@@ -28559,7 +28533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1079" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1079" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1079">
         <v>990</v>
       </c>
@@ -28582,7 +28556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1080" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1080" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1080">
         <v>719</v>
       </c>
@@ -28686,7 +28660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1084" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1084" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1084">
         <v>1719</v>
       </c>
@@ -28764,7 +28738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1087" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1087" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1087">
         <v>1407</v>
       </c>
@@ -28865,7 +28839,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1091" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1091" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1091">
         <v>490</v>
       </c>
@@ -28943,7 +28917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1094" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1094" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1094">
         <v>610</v>
       </c>
@@ -28969,7 +28943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1095" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1095" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1095">
         <v>1147</v>
       </c>
@@ -28992,7 +28966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1096" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1096" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1096">
         <v>1292</v>
       </c>
@@ -29044,7 +29018,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1098" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1098" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1098">
         <v>1141</v>
       </c>
@@ -29070,7 +29044,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1099" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1099" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1099">
         <v>1389</v>
       </c>
@@ -29096,7 +29070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1100" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1100">
         <v>47</v>
       </c>
@@ -29148,7 +29122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1102">
         <v>742</v>
       </c>
@@ -29200,7 +29174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1104">
         <v>212</v>
       </c>
@@ -29330,7 +29304,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1109">
         <v>1320</v>
       </c>
@@ -29460,7 +29434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1114">
         <v>570</v>
       </c>
@@ -29486,7 +29460,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1115">
         <v>63</v>
       </c>
@@ -29564,7 +29538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1118">
         <v>727</v>
       </c>
@@ -29590,7 +29564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1119">
         <v>646</v>
       </c>
@@ -29720,7 +29694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1124">
         <v>1414</v>
       </c>
@@ -29824,7 +29798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1128">
         <v>1372</v>
       </c>
@@ -29902,7 +29876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1131">
         <v>1439</v>
       </c>
@@ -29928,7 +29902,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1132">
         <v>96</v>
       </c>
@@ -30058,7 +30032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1137" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1137">
         <v>68</v>
       </c>
@@ -30136,7 +30110,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1140">
         <v>524</v>
       </c>
@@ -30162,7 +30136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1141">
         <v>1254</v>
       </c>
@@ -30318,7 +30292,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1147" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1147">
         <v>103</v>
       </c>
@@ -30344,7 +30318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1148" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1148">
         <v>1785</v>
       </c>
@@ -30448,7 +30422,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1152" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1152">
         <v>192</v>
       </c>
@@ -30497,7 +30471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1154" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1154">
         <v>816</v>
       </c>
@@ -30653,7 +30627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1160" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1160">
         <v>579</v>
       </c>
@@ -30679,7 +30653,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1161" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1161">
         <v>165</v>
       </c>
@@ -30731,7 +30705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1163" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1163">
         <v>687</v>
       </c>
@@ -30861,7 +30835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1168">
         <v>1437</v>
       </c>
@@ -30965,7 +30939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1172">
         <v>729</v>
       </c>
@@ -31017,7 +30991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1174">
         <v>1075</v>
       </c>
@@ -31043,7 +31017,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1175" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1175">
         <v>1409</v>
       </c>
@@ -31173,7 +31147,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1180" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1180">
         <v>934</v>
       </c>
@@ -31199,7 +31173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1181" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1181">
         <v>486</v>
       </c>
@@ -31277,7 +31251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1184" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1184">
         <v>1206</v>
       </c>
@@ -31329,7 +31303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1186">
         <v>1218</v>
       </c>
@@ -31381,7 +31355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1188" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1188">
         <v>1131</v>
       </c>
@@ -31407,7 +31381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1189" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1189">
         <v>548</v>
       </c>
@@ -31459,7 +31433,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1191">
         <v>231</v>
       </c>
@@ -31563,7 +31537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1195" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1195">
         <v>92</v>
       </c>
@@ -31615,7 +31589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1197" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1197">
         <v>1580</v>
       </c>
@@ -31667,7 +31641,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1199" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1199">
         <v>1420</v>
       </c>
@@ -31771,7 +31745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1203" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1203">
         <v>1022</v>
       </c>
@@ -31979,7 +31953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1211" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1211">
         <v>611</v>
       </c>
@@ -32005,7 +31979,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1212" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1212">
         <v>1308</v>
       </c>
@@ -32161,7 +32135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1218" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1218">
         <v>960</v>
       </c>
@@ -32239,7 +32213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1221" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1221">
         <v>684</v>
       </c>
@@ -32291,7 +32265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1223" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1223">
         <v>1461</v>
       </c>
@@ -32343,7 +32317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1225" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1225">
         <v>687</v>
       </c>
@@ -32395,7 +32369,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1227" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1227">
         <v>1479</v>
       </c>
@@ -32447,7 +32421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1229" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1229">
         <v>1453</v>
       </c>
@@ -32525,7 +32499,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1232" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1232">
         <v>1241</v>
       </c>
@@ -32551,7 +32525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1233" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1233">
         <v>136</v>
       </c>
@@ -32577,7 +32551,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1234" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1234">
         <v>61</v>
       </c>
@@ -32603,7 +32577,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1235" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1235">
         <v>107</v>
       </c>
@@ -32759,7 +32733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1241" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1241">
         <v>1161</v>
       </c>
@@ -32938,7 +32912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1248" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1248">
         <v>1773</v>
       </c>
@@ -32964,7 +32938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1249" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1249">
         <v>1021</v>
       </c>
@@ -33016,7 +32990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1251" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1251">
         <v>560</v>
       </c>
@@ -33042,7 +33016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1252" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1252">
         <v>117</v>
       </c>
@@ -33224,7 +33198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1259">
         <v>500</v>
       </c>
@@ -33276,7 +33250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1261" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1261">
         <v>634</v>
       </c>
@@ -33328,7 +33302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1263" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1263">
         <v>386</v>
       </c>
@@ -33380,7 +33354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1265">
         <v>1451</v>
       </c>
@@ -33406,7 +33380,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1266">
         <v>1694</v>
       </c>
@@ -33432,7 +33406,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1267">
         <v>1257</v>
       </c>
@@ -33484,7 +33458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1269" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1269">
         <v>1283</v>
       </c>
@@ -33614,7 +33588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1274" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1274">
         <v>1096</v>
       </c>
@@ -33744,7 +33718,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1279" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1279">
         <v>1472</v>
       </c>
@@ -33822,7 +33796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1282" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1282">
         <v>1887</v>
       </c>
@@ -33874,7 +33848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1284" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1284">
         <v>1596</v>
       </c>
@@ -33952,7 +33926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1287" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1287">
         <v>1605</v>
       </c>
@@ -33978,7 +33952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1288" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1288">
         <v>1407</v>
       </c>
@@ -34001,7 +33975,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1289" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1289">
         <v>444</v>
       </c>
@@ -34105,7 +34079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1293" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1293">
         <v>983</v>
       </c>
@@ -34235,7 +34209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1298" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1298">
         <v>285</v>
       </c>
@@ -34261,7 +34235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1299" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1299">
         <v>173</v>
       </c>
@@ -34313,7 +34287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1301" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1301">
         <v>247</v>
       </c>
@@ -34391,7 +34365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1304" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1304">
         <v>512</v>
       </c>
@@ -34599,7 +34573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1312" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1312">
         <v>871</v>
       </c>
@@ -34625,7 +34599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1313" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1313">
         <v>1254</v>
       </c>
@@ -34703,7 +34677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1316" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1316">
         <v>1143</v>
       </c>
@@ -34755,7 +34729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1318" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1318">
         <v>18</v>
       </c>
@@ -34807,7 +34781,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1320" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1320">
         <v>178</v>
       </c>
@@ -34911,7 +34885,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1324" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1324">
         <v>1172</v>
       </c>
@@ -35145,7 +35119,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1333" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1333">
         <v>261</v>
       </c>
@@ -35197,7 +35171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1335" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1335">
         <v>1511</v>
       </c>
@@ -35249,7 +35223,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1337" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1337">
         <v>152</v>
       </c>
@@ -35327,7 +35301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1340" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1340">
         <v>370</v>
       </c>
@@ -35353,7 +35327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1341" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1341">
         <v>271</v>
       </c>
@@ -35379,7 +35353,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1342" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1342">
         <v>713</v>
       </c>
@@ -35457,7 +35431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1345" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1345">
         <v>689</v>
       </c>
@@ -35509,7 +35483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1347" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1347">
         <v>411</v>
       </c>
@@ -35587,7 +35561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1350" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1350">
         <v>1460</v>
       </c>
@@ -35691,7 +35665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1354" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1354">
         <v>1582</v>
       </c>
@@ -35847,7 +35821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1360" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1360">
         <v>22</v>
       </c>
@@ -35925,7 +35899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1363" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1363">
         <v>664</v>
       </c>
@@ -35977,7 +35951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1365" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1365" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1365">
         <v>1696</v>
       </c>
@@ -36003,7 +35977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1366" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1366">
         <v>1163</v>
       </c>
@@ -36029,7 +36003,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1367" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1367">
         <v>1405</v>
       </c>
@@ -36237,7 +36211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1375" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1375" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1375">
         <v>1957</v>
       </c>
@@ -36497,7 +36471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1385" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1385">
         <v>804</v>
       </c>
@@ -36523,7 +36497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1386" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1386">
         <v>1225</v>
       </c>
@@ -36679,7 +36653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1392" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1392">
         <v>1861</v>
       </c>
@@ -36861,7 +36835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1399" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1399" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1399">
         <v>1018</v>
       </c>
@@ -36913,7 +36887,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1401" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1401">
         <v>861</v>
       </c>
@@ -36988,7 +36962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1404" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1404">
         <v>1946</v>
       </c>
@@ -37092,7 +37066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1408" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1408">
         <v>1041</v>
       </c>
@@ -37144,7 +37118,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1410" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1410">
         <v>113</v>
       </c>
@@ -37170,7 +37144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1411" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1411">
         <v>569</v>
       </c>
@@ -37222,7 +37196,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1413" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1413" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1413">
         <v>408</v>
       </c>
@@ -37248,7 +37222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1414" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1414">
         <v>1786</v>
       </c>
@@ -37274,7 +37248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1415" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1415">
         <v>402</v>
       </c>
@@ -37326,7 +37300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1417" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1417">
         <v>113</v>
       </c>
@@ -37404,7 +37378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1420" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1420" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1420">
         <v>641</v>
       </c>
@@ -37430,7 +37404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1421" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1421">
         <v>1435</v>
       </c>
@@ -37456,7 +37430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1422" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1422" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1422">
         <v>177</v>
       </c>
@@ -37482,7 +37456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1423" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1423">
         <v>1697</v>
       </c>
@@ -37508,7 +37482,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1424" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1424" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1424">
         <v>1018</v>
       </c>
@@ -37586,7 +37560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1427" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1427">
         <v>1087</v>
       </c>
@@ -37664,7 +37638,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1430" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1430">
         <v>208</v>
       </c>
@@ -37794,7 +37768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1435" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1435">
         <v>1496</v>
       </c>
@@ -37846,7 +37820,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1437" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1437">
         <v>1496</v>
       </c>
@@ -37976,7 +37950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1442" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1442">
         <v>1018</v>
       </c>
@@ -38080,7 +38054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1446" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1446" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1446">
         <v>328</v>
       </c>
@@ -38106,7 +38080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1447" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1447" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1447">
         <v>1216</v>
       </c>
@@ -38132,7 +38106,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1448" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1448" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1448">
         <v>1571</v>
       </c>
@@ -38184,7 +38158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1450" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1450" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1450">
         <v>617</v>
       </c>
@@ -38236,7 +38210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1452" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1452" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1452">
         <v>1336</v>
       </c>
@@ -38288,7 +38262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1454" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1454" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1454">
         <v>1786</v>
       </c>
@@ -38522,7 +38496,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1463" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1463">
         <v>812</v>
       </c>
@@ -38548,7 +38522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1464">
         <v>1871</v>
       </c>
@@ -38678,7 +38652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1469" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1469" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1469">
         <v>1216</v>
       </c>
@@ -38756,7 +38730,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1472" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1472">
         <v>242</v>
       </c>
@@ -39016,7 +38990,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1482" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1482">
         <v>1427</v>
       </c>
@@ -39042,7 +39016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1483" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1483">
         <v>338</v>
       </c>
@@ -39068,7 +39042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1484" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1484">
         <v>597</v>
       </c>
@@ -39172,7 +39146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1488" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1488">
         <v>899</v>
       </c>
@@ -39198,7 +39172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1489" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1489">
         <v>1225</v>
       </c>
@@ -39432,7 +39406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1498" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1498">
         <v>1906</v>
       </c>
@@ -39458,7 +39432,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1499" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1499">
         <v>929</v>
       </c>
@@ -39614,7 +39588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1505" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1505">
         <v>432</v>
       </c>
@@ -39692,7 +39666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1508" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1508">
         <v>419</v>
       </c>
@@ -39744,7 +39718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1510" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1510">
         <v>138</v>
       </c>
@@ -39796,7 +39770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1512" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1512" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1512">
         <v>94</v>
       </c>
@@ -39874,7 +39848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1515" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1515" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1515">
         <v>406</v>
       </c>
@@ -40056,7 +40030,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1522" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1522" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1522">
         <v>1251</v>
       </c>
@@ -40082,7 +40056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1523" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1523" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1523">
         <v>1216</v>
       </c>
@@ -40160,7 +40134,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1526" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1526" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1526">
         <v>1041</v>
       </c>
@@ -40186,7 +40160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1527" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1527">
         <v>344</v>
       </c>
@@ -40212,7 +40186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1528" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1528" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1528">
         <v>28</v>
       </c>
@@ -40264,7 +40238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1530" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1530" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1530">
         <v>1416</v>
       </c>
@@ -40420,7 +40394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1536" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1536" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1536">
         <v>1761</v>
       </c>
@@ -40472,7 +40446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1538" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1538" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1538">
         <v>1500</v>
       </c>
@@ -40498,7 +40472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1539" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1539" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1539">
         <v>43</v>
       </c>
@@ -40550,7 +40524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1541" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1541" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1541">
         <v>225</v>
       </c>
@@ -40654,7 +40628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1545" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1545">
         <v>732</v>
       </c>
@@ -40706,7 +40680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1547" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1547">
         <v>473</v>
       </c>
@@ -40732,7 +40706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1548" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1548">
         <v>1953</v>
       </c>
@@ -40836,7 +40810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1552" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1552">
         <v>1407</v>
       </c>
@@ -40859,7 +40833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1553" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1553">
         <v>1647</v>
       </c>
@@ -40911,7 +40885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1555" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1555">
         <v>135</v>
       </c>
@@ -41015,7 +40989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1559" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1559">
         <v>626</v>
       </c>
@@ -41067,7 +41041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1561" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1561" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1561">
         <v>650</v>
       </c>
@@ -41119,7 +41093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1563" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1563" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1563">
         <v>1615</v>
       </c>
@@ -41145,7 +41119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1564" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1564" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1564">
         <v>285</v>
       </c>
@@ -41171,7 +41145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1565" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1565" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1565">
         <v>398</v>
       </c>
@@ -41301,7 +41275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1570" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1570" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1570">
         <v>1521</v>
       </c>
@@ -41327,7 +41301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1571" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1571" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1571">
         <v>392</v>
       </c>
@@ -41353,7 +41327,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1572" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1572" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1572">
         <v>228</v>
       </c>
@@ -41405,7 +41379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1574" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1574" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1574">
         <v>1035</v>
       </c>
@@ -41457,7 +41431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1576" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1576" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1576">
         <v>178</v>
       </c>
@@ -41561,7 +41535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1580" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1580" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1580">
         <v>838</v>
       </c>
@@ -41587,7 +41561,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1581" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1581" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1581">
         <v>923</v>
       </c>
@@ -41691,7 +41665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1585" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1585" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1585">
         <v>833</v>
       </c>
@@ -41717,7 +41691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1586" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1586" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1586">
         <v>305</v>
       </c>
@@ -41743,7 +41717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1587" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1587" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1587">
         <v>113</v>
       </c>
@@ -41873,7 +41847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1592" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1592" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1592">
         <v>1475</v>
       </c>
@@ -42055,7 +42029,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1599" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1599" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1599">
         <v>1301</v>
       </c>
@@ -42104,7 +42078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1601" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1601" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1601">
         <v>1161</v>
       </c>
@@ -42205,7 +42179,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1605" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1605" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1605">
         <v>1843</v>
       </c>
@@ -42387,7 +42361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1612" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1612" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1612">
         <v>1995</v>
       </c>
@@ -42413,7 +42387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1613" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1613" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1613">
         <v>805</v>
       </c>
@@ -42439,7 +42413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1614" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1614" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1614">
         <v>1151</v>
       </c>
@@ -42670,7 +42644,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1623" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1623" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1623">
         <v>1385</v>
       </c>
@@ -42696,7 +42670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1624" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1624" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1624">
         <v>1416</v>
       </c>
@@ -42722,7 +42696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1625" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1625" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1625">
         <v>1255</v>
       </c>
@@ -42774,7 +42748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1627" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1627" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1627">
         <v>521</v>
       </c>
@@ -42904,7 +42878,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1632" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1632" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1632">
         <v>750</v>
       </c>
@@ -42930,7 +42904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1633" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1633" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1633">
         <v>532</v>
       </c>
@@ -43060,7 +43034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1638" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1638" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1638">
         <v>402</v>
       </c>
@@ -43138,7 +43112,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1641" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1641" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1641">
         <v>1077</v>
       </c>
@@ -43164,7 +43138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1642" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1642" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1642">
         <v>814</v>
       </c>
@@ -43216,7 +43190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1644" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1644" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1644">
         <v>1486</v>
       </c>
@@ -43242,7 +43216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1645" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1645" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1645">
         <v>1540</v>
       </c>
@@ -43268,7 +43242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1646" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1646" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1646">
         <v>517</v>
       </c>
@@ -43372,7 +43346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1650" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1650" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1650">
         <v>269</v>
       </c>
@@ -43658,7 +43632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1661" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1661" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1661">
         <v>342</v>
       </c>
@@ -43840,7 +43814,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1668" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1668" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1668">
         <v>302</v>
       </c>
@@ -43866,7 +43840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1669" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1669" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1669">
         <v>955</v>
       </c>
@@ -43918,7 +43892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1671" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1671" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1671">
         <v>687</v>
       </c>
@@ -44022,7 +43996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1675" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1675" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1675">
         <v>1578</v>
       </c>
@@ -44100,7 +44074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1678" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1678" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1678">
         <v>658</v>
       </c>
@@ -44178,7 +44152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1681" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1681" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1681">
         <v>1314</v>
       </c>
@@ -44282,7 +44256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1685" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1685" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1685">
         <v>697</v>
       </c>
@@ -44308,7 +44282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1686" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1686" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1686">
         <v>1734</v>
       </c>
@@ -44386,7 +44360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1689" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1689" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1689">
         <v>643</v>
       </c>
@@ -44542,7 +44516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1695" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1695" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1695">
         <v>946</v>
       </c>
@@ -44565,7 +44539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1696" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1696" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1696">
         <v>1495</v>
       </c>
@@ -44591,7 +44565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1697" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1697" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1697">
         <v>944</v>
       </c>
@@ -44643,7 +44617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1699" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1699" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1699">
         <v>877</v>
       </c>
@@ -44773,7 +44747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1704" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1704" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1704">
         <v>178</v>
       </c>
@@ -44825,7 +44799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1706" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1706" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1706">
         <v>1640</v>
       </c>
@@ -45059,7 +45033,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1715" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1715" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1715">
         <v>1824</v>
       </c>
@@ -45108,7 +45082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1717" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1717" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1717">
         <v>464</v>
       </c>
@@ -45134,7 +45108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1718" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1718" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1718">
         <v>402</v>
       </c>
@@ -45394,7 +45368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1728" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1728" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1728">
         <v>1811</v>
       </c>
@@ -45446,7 +45420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1730" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1730" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1730">
         <v>1333</v>
       </c>
@@ -45524,7 +45498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1733" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1733" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1733">
         <v>1405</v>
       </c>
@@ -45628,7 +45602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1737" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1737" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1737">
         <v>1257</v>
       </c>
@@ -45654,7 +45628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1738" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1738" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1738">
         <v>829</v>
       </c>
@@ -45677,7 +45651,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1739" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1739" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1739">
         <v>1393</v>
       </c>
@@ -45703,7 +45677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1740" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1740" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1740">
         <v>1679</v>
       </c>
@@ -45807,7 +45781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1744" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1744" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1744">
         <v>95</v>
       </c>
@@ -45859,7 +45833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1746" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1746" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1746">
         <v>1946</v>
       </c>
@@ -45963,7 +45937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1750" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1750" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1750">
         <v>53</v>
       </c>
@@ -46015,7 +45989,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1752" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1752" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1752">
         <v>109</v>
       </c>
@@ -46041,7 +46015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1753" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1753" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1753">
         <v>1761</v>
       </c>
@@ -46119,7 +46093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1756" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1756" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1756">
         <v>285</v>
       </c>
@@ -46197,7 +46171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1759" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1759" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1759">
         <v>1690</v>
       </c>
@@ -46249,7 +46223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1761" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1761" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1761">
         <v>628</v>
       </c>
@@ -46301,7 +46275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1763" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1763" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1763">
         <v>1455</v>
       </c>
@@ -46327,7 +46301,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1764" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1764" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1764">
         <v>1465</v>
       </c>
@@ -46483,7 +46457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1770" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1770" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1770">
         <v>1969</v>
       </c>
@@ -46535,7 +46509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1772" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1772" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1772">
         <v>1511</v>
       </c>
@@ -46665,7 +46639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1777" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1777" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1777">
         <v>1511</v>
       </c>
@@ -46743,7 +46717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1780" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1780" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1780">
         <v>550</v>
       </c>
@@ -46795,7 +46769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1782" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1782" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1782">
         <v>934</v>
       </c>
@@ -46899,7 +46873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1786" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1786" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1786">
         <v>1432</v>
       </c>
@@ -47081,7 +47055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1793" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1793" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1793">
         <v>1399</v>
       </c>
@@ -47133,7 +47107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1795" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1795" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1795">
         <v>1560</v>
       </c>
@@ -47159,7 +47133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1796" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1796" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1796">
         <v>1606</v>
       </c>
@@ -47289,7 +47263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1801" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1801" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1801">
         <v>686</v>
       </c>
@@ -47471,7 +47445,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1808" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1808" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1808">
         <v>99</v>
       </c>
@@ -47575,7 +47549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1812" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1812" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1812">
         <v>327</v>
       </c>
@@ -47653,7 +47627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1815" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1815" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1815">
         <v>527</v>
       </c>
@@ -47679,7 +47653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1816" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1816" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1816">
         <v>254</v>
       </c>
@@ -47887,7 +47861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1824" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1824" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1824">
         <v>1320</v>
       </c>
@@ -47913,7 +47887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1825" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1825" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1825">
         <v>1405</v>
       </c>
@@ -48043,7 +48017,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1830" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1830" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1830">
         <v>386</v>
       </c>
@@ -48069,7 +48043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1831" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1831" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1831">
         <v>1821</v>
       </c>
@@ -48121,7 +48095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1833" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1833" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1833">
         <v>1253</v>
       </c>
@@ -48225,7 +48199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1837" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1837" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1837">
         <v>1840</v>
       </c>
@@ -48303,7 +48277,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1840" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1840" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1840">
         <v>560</v>
       </c>
@@ -48329,7 +48303,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1841" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1841" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1841">
         <v>1407</v>
       </c>
@@ -48352,7 +48326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1842" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1842" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1842">
         <v>836</v>
       </c>
@@ -48404,7 +48378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1844" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1844" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1844">
         <v>1977</v>
       </c>
@@ -48508,7 +48482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1848" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1848" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1848">
         <v>1316</v>
       </c>
@@ -48612,7 +48586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1852" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1852" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1852">
         <v>270</v>
       </c>
@@ -48716,7 +48690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1856" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1856" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1856">
         <v>1021</v>
       </c>
@@ -48794,7 +48768,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1859" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1859" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1859">
         <v>1453</v>
       </c>
@@ -48898,7 +48872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1863" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1863" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1863">
         <v>1109</v>
       </c>
@@ -48924,7 +48898,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1864" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1864" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1864">
         <v>1031</v>
       </c>
@@ -48950,7 +48924,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1865" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1865" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1865">
         <v>1337</v>
       </c>
@@ -49080,7 +49054,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1870" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1870" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1870">
         <v>1244</v>
       </c>
@@ -49158,7 +49132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1873" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1873" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1873">
         <v>35</v>
       </c>
@@ -49184,7 +49158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1874" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1874" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1874">
         <v>1530</v>
       </c>
@@ -49314,7 +49288,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1879" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1879" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1879">
         <v>1735</v>
       </c>
@@ -49392,7 +49366,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1882" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1882" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1882">
         <v>504</v>
       </c>
@@ -49418,7 +49392,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1883" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1883" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1883">
         <v>1796</v>
       </c>
@@ -49470,7 +49444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1885" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1885" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1885">
         <v>1511</v>
       </c>
@@ -49600,7 +49574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1890" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1890" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1890">
         <v>670</v>
       </c>
@@ -49730,7 +49704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1895" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1895" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1895">
         <v>805</v>
       </c>
@@ -49808,7 +49782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1898" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1898" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1898">
         <v>1934</v>
       </c>
@@ -49834,7 +49808,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1899" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1899" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1899">
         <v>897</v>
       </c>
@@ -49912,7 +49886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1902" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1902" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1902">
         <v>488</v>
       </c>
@@ -49990,7 +49964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1905" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1905" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1905">
         <v>1241</v>
       </c>
@@ -50094,7 +50068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1909" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1909" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1909">
         <v>1674</v>
       </c>
@@ -50120,7 +50094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1910" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1910" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1910">
         <v>275</v>
       </c>
@@ -50146,7 +50120,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1911" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1911" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1911">
         <v>1840</v>
       </c>
@@ -50198,7 +50172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1913" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1913" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1913">
         <v>1817</v>
       </c>
@@ -50224,7 +50198,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1914" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1914" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1914">
         <v>79</v>
       </c>
@@ -50250,7 +50224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1915" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1915" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1915">
         <v>1250</v>
       </c>
@@ -50380,7 +50354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1920" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1920" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1920">
         <v>1550</v>
       </c>
@@ -50406,7 +50380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1921" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1921" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1921">
         <v>1452</v>
       </c>
@@ -50458,7 +50432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1923" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1923" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1923">
         <v>1265</v>
       </c>
@@ -50666,7 +50640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1931" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1931" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1931">
         <v>1293</v>
       </c>
@@ -50718,7 +50692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1933" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1933" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1933">
         <v>1689</v>
       </c>
@@ -50770,7 +50744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1935" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1935" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1935">
         <v>504</v>
       </c>
@@ -50900,7 +50874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1940" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1940" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1940">
         <v>1810</v>
       </c>
@@ -50926,7 +50900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1941" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1941" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1941">
         <v>47</v>
       </c>
@@ -51001,7 +50975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1944" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1944" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1944">
         <v>1821</v>
       </c>
@@ -51131,7 +51105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1949" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1949" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1949">
         <v>1008</v>
       </c>
@@ -51157,7 +51131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1950" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1950" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1950">
         <v>1018</v>
       </c>
@@ -51261,7 +51235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1954" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1954" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1954">
         <v>677</v>
       </c>
@@ -51287,7 +51261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1955" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1955" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1955">
         <v>1407</v>
       </c>
@@ -51362,7 +51336,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1958" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1958" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1958">
         <v>650</v>
       </c>
@@ -51414,7 +51388,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1960" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1960" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1960">
         <v>203</v>
       </c>
@@ -51440,7 +51414,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1961" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1961" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1961">
         <v>1435</v>
       </c>
@@ -51466,7 +51440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1962" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1962" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1962">
         <v>1967</v>
       </c>
@@ -51544,7 +51518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1965" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1965" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1965">
         <v>1700</v>
       </c>
@@ -51570,7 +51544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1966" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1966" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1966">
         <v>1688</v>
       </c>
@@ -51648,7 +51622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1969" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1969" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1969">
         <v>178</v>
       </c>
@@ -51674,7 +51648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1970" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1970" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1970">
         <v>1637</v>
       </c>
@@ -51752,7 +51726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1973" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1973" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1973">
         <v>412</v>
       </c>
@@ -51908,7 +51882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1979" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1979" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1979">
         <v>1775</v>
       </c>
@@ -51934,7 +51908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1980" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1980" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1980">
         <v>967</v>
       </c>
@@ -52009,7 +51983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1983" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1983" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1983">
         <v>1031</v>
       </c>
@@ -52035,7 +52009,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1984" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1984" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1984">
         <v>1161</v>
       </c>
@@ -52162,7 +52136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1989" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1989" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1989">
         <v>1866</v>
       </c>
@@ -52188,7 +52162,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1990" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1990" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1990">
         <v>303</v>
       </c>
@@ -52266,7 +52240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1993" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1993" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1993">
         <v>1632</v>
       </c>
@@ -52292,7 +52266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1994" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1994" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1994">
         <v>644</v>
       </c>
@@ -52500,7 +52474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2002" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2002" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2002">
         <v>687</v>
       </c>
@@ -52604,7 +52578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2006" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2006" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2006">
         <v>922</v>
       </c>
@@ -52630,7 +52604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2007" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2007" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2007">
         <v>564</v>
       </c>
@@ -52656,7 +52630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2008" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2008" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2008">
         <v>1295</v>
       </c>
@@ -52682,7 +52656,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2009" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2009" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2009">
         <v>814</v>
       </c>
@@ -52734,7 +52708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2011" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2011" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2011">
         <v>1280</v>
       </c>
@@ -52760,7 +52734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2012" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2012" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2012">
         <v>203</v>
       </c>
@@ -52864,7 +52838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2016" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2016" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2016">
         <v>748</v>
       </c>
@@ -52916,7 +52890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2018" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2018" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2018">
         <v>1525</v>
       </c>
@@ -53228,7 +53202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2030" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2030" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2030">
         <v>646</v>
       </c>
@@ -53332,7 +53306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2034" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2034" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2034">
         <v>1206</v>
       </c>
@@ -53384,7 +53358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2036" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2036" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2036">
         <v>798</v>
       </c>
@@ -53410,7 +53384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2037" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2037" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2037">
         <v>1099</v>
       </c>
@@ -53566,7 +53540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2043" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2043" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2043">
         <v>1092</v>
       </c>
@@ -53618,7 +53592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2045" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2045" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2045">
         <v>1509</v>
       </c>
@@ -53644,7 +53618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2046" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2046" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2046">
         <v>825</v>
       </c>
@@ -53670,7 +53644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2047" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2047" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2047">
         <v>1943</v>
       </c>
@@ -53722,7 +53696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2049" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2049" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2049">
         <v>907</v>
       </c>
@@ -53956,7 +53930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2058" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2058" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2058">
         <v>540</v>
       </c>
@@ -54346,7 +54320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2073" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2073" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2073">
         <v>824</v>
       </c>
@@ -54398,7 +54372,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2075" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2075" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2075">
         <v>687</v>
       </c>
@@ -54476,7 +54450,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2078" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2078" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2078">
         <v>644</v>
       </c>
@@ -54528,7 +54502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2080" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2080" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2080">
         <v>1590</v>
       </c>
@@ -54580,7 +54554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2082" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2082" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2082">
         <v>1877</v>
       </c>
@@ -54632,7 +54606,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2084" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2084" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2084">
         <v>991</v>
       </c>
@@ -54788,7 +54762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2090" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2090" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2090">
         <v>1343</v>
       </c>
@@ -54814,7 +54788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2091" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2091" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2091">
         <v>1920</v>
       </c>
@@ -54840,7 +54814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2092" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2092" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2092">
         <v>1827</v>
       </c>
@@ -54892,7 +54866,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2094" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2094" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2094">
         <v>1096</v>
       </c>
@@ -54918,7 +54892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2095" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2095" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2095">
         <v>476</v>
       </c>
@@ -54970,7 +54944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2097" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2097" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2097">
         <v>247</v>
       </c>
@@ -55126,7 +55100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2103">
         <v>672</v>
       </c>
@@ -55152,7 +55126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2104">
         <v>1674</v>
       </c>
@@ -55178,7 +55152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2105">
         <v>1169</v>
       </c>
@@ -55204,7 +55178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2106">
         <v>910</v>
       </c>
@@ -55230,7 +55204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2107">
         <v>342</v>
       </c>
@@ -55256,7 +55230,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2108">
         <v>238</v>
       </c>
@@ -55282,7 +55256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2109">
         <v>1935</v>
       </c>
@@ -55412,7 +55386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2114">
         <v>494</v>
       </c>
@@ -55438,7 +55412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2115">
         <v>1647</v>
       </c>
@@ -55464,7 +55438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2116">
         <v>1689</v>
       </c>
@@ -55542,7 +55516,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2119">
         <v>1025</v>
       </c>
@@ -55568,7 +55542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2120">
         <v>1254</v>
       </c>
@@ -55594,7 +55568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2121">
         <v>488</v>
       </c>
@@ -55646,7 +55620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2123">
         <v>1383</v>
       </c>
@@ -55698,7 +55672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2125">
         <v>1449</v>
       </c>
@@ -56062,7 +56036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2139">
         <v>1040</v>
       </c>
@@ -56114,7 +56088,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2141">
         <v>1425</v>
       </c>
@@ -56140,7 +56114,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2142">
         <v>676</v>
       </c>
@@ -56192,7 +56166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2144" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2144">
         <v>1620</v>
       </c>
@@ -56218,7 +56192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2145" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2145">
         <v>1647</v>
       </c>
@@ -56530,7 +56504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2157" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2157">
         <v>1068</v>
       </c>
@@ -56582,7 +56556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2159" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2159">
         <v>79</v>
       </c>
@@ -56738,7 +56712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2165">
         <v>697</v>
       </c>
@@ -56816,7 +56790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2168">
         <v>90</v>
       </c>
@@ -56842,7 +56816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2169" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2169">
         <v>1571</v>
       </c>
@@ -56868,7 +56842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2170" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2170">
         <v>104</v>
       </c>
@@ -56894,7 +56868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2171" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2171">
         <v>1585</v>
       </c>
@@ -56920,7 +56894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2172">
         <v>1105</v>
       </c>
@@ -56946,7 +56920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2173" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2173">
         <v>315</v>
       </c>
@@ -56972,7 +56946,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2174">
         <v>1182</v>
       </c>
@@ -57024,7 +56998,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2176" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2176">
         <v>585</v>
       </c>
@@ -57284,7 +57258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2186">
         <v>35</v>
       </c>
@@ -57310,7 +57284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2187" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2187">
         <v>1410</v>
       </c>
@@ -57518,7 +57492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2195" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2195">
         <v>1864</v>
       </c>
@@ -57596,7 +57570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2198" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2198">
         <v>1534</v>
       </c>
@@ -57700,7 +57674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2202" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2202">
         <v>1304</v>
       </c>
@@ -57778,7 +57752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2205" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2205">
         <v>1023</v>
       </c>
@@ -57830,7 +57804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2207" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2207">
         <v>719</v>
       </c>
@@ -57882,7 +57856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2209" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2209">
         <v>160</v>
       </c>
@@ -57908,7 +57882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2210" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2210">
         <v>883</v>
       </c>
@@ -57960,7 +57934,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2212" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2212">
         <v>1760</v>
       </c>
@@ -57986,7 +57960,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2213" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2213">
         <v>1461</v>
       </c>
@@ -58142,7 +58116,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2219" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2219">
         <v>1493</v>
       </c>
@@ -58220,7 +58194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2222" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2222">
         <v>398</v>
       </c>
@@ -58272,7 +58246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2224" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2224">
         <v>401</v>
       </c>
@@ -58402,7 +58376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2229" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2229">
         <v>814</v>
       </c>
@@ -58428,7 +58402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2230" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2230">
         <v>730</v>
       </c>
@@ -58532,7 +58506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2234" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2234">
         <v>752</v>
       </c>
@@ -58558,7 +58532,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2235" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2235">
         <v>560</v>
       </c>
@@ -58584,7 +58558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2236" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2236">
         <v>1486</v>
       </c>
@@ -58610,7 +58584,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2237" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2237">
         <v>910</v>
       </c>
@@ -58714,7 +58688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2241" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2241">
         <v>988</v>
       </c>
@@ -58818,7 +58792,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2245" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2245">
         <v>1945</v>
       </c>
@@ -58844,7 +58818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2246" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2246">
         <v>527</v>
       </c>
@@ -58870,7 +58844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2247" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2247">
         <v>1854</v>
       </c>
@@ -58896,7 +58870,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2248" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2248">
         <v>1347</v>
       </c>
@@ -58974,7 +58948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2251" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2251">
         <v>1293</v>
       </c>
@@ -59000,7 +58974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2252" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2252">
         <v>1633</v>
       </c>
@@ -59026,7 +59000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2253" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2253">
         <v>1940</v>
       </c>
@@ -59078,7 +59052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2255" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2255">
         <v>1425</v>
       </c>
@@ -59104,7 +59078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2256" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2256">
         <v>393</v>
       </c>
@@ -59130,7 +59104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2257" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2257">
         <v>1664</v>
       </c>
@@ -59208,7 +59182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2260" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2260">
         <v>1158</v>
       </c>
@@ -59312,7 +59286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2264">
         <v>946</v>
       </c>
@@ -59335,7 +59309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2265">
         <v>401</v>
       </c>
@@ -59361,7 +59335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2266">
         <v>634</v>
       </c>
@@ -59517,7 +59491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2272" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2272">
         <v>1647</v>
       </c>
@@ -59569,7 +59543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2274" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2274">
         <v>1970</v>
       </c>
@@ -59595,7 +59569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2275" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2275">
         <v>396</v>
       </c>
@@ -59725,7 +59699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2280" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2280">
         <v>967</v>
       </c>
@@ -59748,7 +59722,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2281" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2281">
         <v>449</v>
       </c>
@@ -59826,7 +59800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2284" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2284">
         <v>519</v>
       </c>
@@ -59930,7 +59904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2288" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2288">
         <v>188</v>
       </c>
@@ -59956,7 +59930,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2289" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2289">
         <v>1225</v>
       </c>
@@ -60008,7 +59982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2291" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2291">
         <v>697</v>
       </c>
@@ -60164,7 +60138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2297" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2297">
         <v>839</v>
       </c>
@@ -60317,7 +60291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2303" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2303">
         <v>838</v>
       </c>
@@ -60369,7 +60343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2305" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2305">
         <v>1853</v>
       </c>
